--- a/raw data/Cycle_2.xlsx
+++ b/raw data/Cycle_2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\youss\Documents\2_Academics_Career\3_INTERNSHIP\7_Research\Orthopedic DVT audit submission\Orthopedic_Thromboprophylaxis_Audit\raw data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E821E373-23CA-4D42-A2A3-4330DE43C2FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D59DF5F1-7248-40AE-B5CC-AF1FD7CF2CA6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" xr2:uid="{174317AD-B72F-4F64-98FA-128430B9000B}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="155">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1777" uniqueCount="155">
   <si>
     <t>Age</t>
   </si>
@@ -2993,6 +2993,9 @@
       <c r="Q27">
         <v>15</v>
       </c>
+      <c r="R27" t="s">
+        <v>51</v>
+      </c>
       <c r="S27" t="s">
         <v>12</v>
       </c>
